--- a/docs/lem/files/xslope_hassiotis_p1.xlsx
+++ b/docs/lem/files/xslope_hassiotis_p1.xlsx
@@ -5601,15 +5601,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>50000.0</v>
-      </c>
-      <c r="N11" s="3">
-        <v>0.4</v>
-      </c>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t>none</t>
@@ -5645,13 +5639,13 @@
         <v>0.0</v>
       </c>
       <c r="AA11" s="3">
-        <v>1.2</v>
+        <v>0.0</v>
       </c>
       <c r="AB11" s="3">
-        <v>1.8</v>
+        <v>0.0</v>
       </c>
       <c r="AC11" s="3">
-        <v>2.744</v>
+        <v>0.0</v>
       </c>
       <c r="AD11" s="3">
         <v>0.0</v>

--- a/docs/lem/files/xslope_hassiotis_p1.xlsx
+++ b/docs/lem/files/xslope_hassiotis_p1.xlsx
@@ -2641,7 +2641,26 @@
       </c>
       <c r="H2" s="40" t="inlineStr">
         <is>
-          <t>qp</t>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>q</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>p</t>
+          </r>
         </is>
       </c>
       <c r="I2" s="40" t="inlineStr">
@@ -5371,7 +5390,23 @@
       </c>
       <c r="D10" s="48" t="inlineStr">
         <is>
-          <t>gsat</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>g</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+            </rPr>
+            <t>sat</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="44" t="inlineStr">
@@ -5486,12 +5521,64 @@
       </c>
       <c r="AA10" s="46" t="inlineStr">
         <is>
-          <t>s(g)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>g</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="AB10" s="46" t="inlineStr">
         <is>
-          <t>s(c)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(c)</t>
+          </r>
         </is>
       </c>
       <c r="AC10" s="47" t="inlineStr">
@@ -5501,17 +5588,70 @@
       </c>
       <c r="AD10" s="46" t="inlineStr">
         <is>
-          <t>s(c/p)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(c/p)</t>
+          </r>
         </is>
       </c>
       <c r="AE10" s="46" t="inlineStr">
         <is>
-          <t>s(d)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(d)</t>
+          </r>
         </is>
       </c>
       <c r="AF10" s="47" t="inlineStr">
         <is>
-          <t>s(psi)</t>
+          <r>
+            <t>s(</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+            </rPr>
+            <t>psi</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="AG10" s="23" t="inlineStr">
